--- a/design/TitlesMod-Design.xlsx
+++ b/design/TitlesMod-Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\IdeaProjects\TitlesMod\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10F9C165-EB34-490F-B1D4-4817528B3CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{263BBEF4-E48C-4268-AC7C-1B61D6FC95D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5112" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{201FBAB2-EA2D-47D2-8054-6946E4F5BAE7}"/>
+    <workbookView xWindow="5112" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{5BD3E99C-9A34-4EAF-96BE-896F56304FA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3544" uniqueCount="1771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3559" uniqueCount="1784">
   <si>
     <t>Field</t>
   </si>
@@ -3895,13 +3895,13 @@
     <t>No - hard caps per attribute</t>
   </si>
   <si>
-    <t>DECIDED - hard caps - see Balance Model</t>
-  </si>
-  <si>
-    <t>Second safety net. Clamps the final summed total including scarce contributions. Stacked damage resistances approaching immunity is the classic way this genre breaks.</t>
-  </si>
-  <si>
-    <t>Clamp at modifier-application time not at equip time</t>
+    <t>DECIDED - hard caps on the Titles-sourced total - see Balance Model</t>
+  </si>
+  <si>
+    <t>Second safety net. Clamps the total this mod contributes - equipped plus scarce - NOT the player's final attribute value. Stacked damage resistances approaching immunity is the classic way this genre breaks.</t>
+  </si>
+  <si>
+    <t>Clamp at modifier-application time not at equip time. Apply one modifier per attribute and never read the player's final attribute value.</t>
   </si>
   <si>
     <t>Single player parity</t>
@@ -4375,6 +4375,27 @@
     <t>Core must load and play correctly with every integration absent. Test that case explicitly - it is the common one for most users.</t>
   </si>
   <si>
+    <t>Stacking with other stat mods</t>
+  </si>
+  <si>
+    <t>Do our caps limit our own contribution or the player's final stat?</t>
+  </si>
+  <si>
+    <t>Clamp the player's final attribute value</t>
+  </si>
+  <si>
+    <t>Clamp only what Titles contributes</t>
+  </si>
+  <si>
+    <t>DECIDED - clamp only the Titles-sourced total</t>
+  </si>
+  <si>
+    <t>Every pack we target already grants attributes - Just Leveling and Passive Skill Tree in Soulrend - skill tree and divine blessings in Cisco's. Clamping the final value would grant nothing in those packs or actively strip health another mod gave - a bug report blaming us for their mod. We stack on top and stay out of the way.</t>
+  </si>
+  <si>
+    <t>Attribute code must never call player.getAttributeValue() to make a decision. Sum our own effects - clamp - apply. The derived-UUID rule from Forward compat - attribute ids is what makes our modifiers identifiable.</t>
+  </si>
+  <si>
     <t>Phase</t>
   </si>
   <si>
@@ -5173,6 +5194,15 @@
     <t>Second safety net. Even inside 40 points a player could dump everything into one attribute. Hard caps mean no single stat can run away.</t>
   </si>
   <si>
+    <t>Stacking with other mods</t>
+  </si>
+  <si>
+    <t>Titles ADDS on top of whatever other mods grant. It never reads - clamps or overrides another mod's contribution.</t>
+  </si>
+  <si>
+    <t>DECIDED. Every integration target already ships its own levelling or stat system - Just Leveling and Passive Skill Tree in Soulrend - skill tree - origins and divine blessings in Cisco's Dragonfyre. The caps below limit what THIS mod contributes - not what the player ends up with. Reading the player's final attribute value would either zero out our bonus in those packs or clamp down health another mod granted. Additive-only is what makes the mod safe to drop into any pack.</t>
+  </si>
+  <si>
     <t>Sample builds at the 40-point cap</t>
   </si>
   <si>
@@ -5347,7 +5377,16 @@
     <t>Enforce the budget cap in the equip handler on the SERVER. Refuse the equip and send a message. Never trust the client.</t>
   </si>
   <si>
-    <t>Enforce per-attribute caps at modifier-application time - after summing all equipped and scarce contributions - by clamping the final total.</t>
+    <t>Enforce per-attribute caps on the TITLES-SOURCED total only. Sum the contributions from equipped and scarce titles - clamp that sum to the cap - then apply it. Never read the player's final attribute value.</t>
+  </si>
+  <si>
+    <t>player.getAttributeValue() returns the total from every mod and is the wrong number. Our own modifiers are identifiable by their derived UUIDs - we never need to inspect anyone else's.</t>
+  </si>
+  <si>
+    <t>Apply ONE modifier per attribute per player - recomputed whenever the equipped set changes. Not one modifier per title.</t>
+  </si>
+  <si>
+    <t>Clamping becomes plain arithmetic before touching the attribute map at all. Unequip is a single removeModifier with a UUID we can always derive. We replace rather than accumulate - so a crash or a bad relog cannot leave orphaned modifiers silently stacking buffs.</t>
   </si>
   <si>
     <t>Show remaining budget live in the Titles screen as "31 / 40". Players will optimise against it and that is the fun.</t>
@@ -5831,7 +5870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EFCD237-B230-4ED9-B256-5BC667858E00}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{768CCA91-BABD-464E-8EB5-4030549F8955}">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6114,34 +6153,36 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{0EFCD237-B230-4ED9-B256-5BC667858E00}"/>
+  <autoFilter ref="A1:C1" xr:uid="{768CCA91-BABD-464E-8EB5-4030549F8955}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E70BD82A-53AC-4758-97EB-B4C6645F72A7}">
-  <dimension ref="A1:D40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C219768B-C22C-4C70-91C6-145F16566594}">
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="10.77734375" customWidth="1"/>
+    <col min="1" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1680</v>
+        <v>1687</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1681</v>
+        <v>1688</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1192</v>
       </c>
@@ -6149,21 +6190,21 @@
         <v>430</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1682</v>
+        <v>1689</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>1683</v>
+        <v>1690</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1684</v>
+        <v>1691</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1685</v>
+        <v>1692</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -6171,125 +6212,125 @@
     </row>
     <row r="4" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1686</v>
+        <v>1693</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1687</v>
+        <v>1694</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1688</v>
+        <v>1695</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1267</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1689</v>
+        <v>1696</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1691</v>
+        <v>1698</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1692</v>
+        <v>1699</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1693</v>
+        <v>1700</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1694</v>
+        <v>1701</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1695</v>
+        <v>1702</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1696</v>
+        <v>1703</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1697</v>
+        <v>1704</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1698</v>
+        <v>1705</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1699</v>
+        <v>1706</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1700</v>
+        <v>1707</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1701</v>
+        <v>1708</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1702</v>
+        <v>1709</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>1710</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>14</v>
+        <v>1711</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>14</v>
+        <v>1712</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1703</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1704</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1705</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1706</v>
+        <v>1713</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1707</v>
+        <v>1714</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1708</v>
+        <v>1715</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -6297,111 +6338,111 @@
     </row>
     <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1709</v>
+        <v>1716</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1710</v>
+        <v>1717</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1711</v>
+        <v>1718</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1712</v>
+        <v>1719</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1713</v>
+        <v>1720</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1714</v>
+        <v>1721</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1716</v>
+        <v>1723</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1717</v>
+        <v>1724</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1718</v>
+        <v>1725</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1719</v>
+        <v>1726</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1720</v>
+        <v>1727</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>1728</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>1729</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>14</v>
+        <v>1730</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1721</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1722</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1724</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1725</v>
-      </c>
       <c r="D19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>1726</v>
+        <v>1733</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1024</v>
+        <v>1734</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1727</v>
+        <v>1735</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
@@ -6409,125 +6450,125 @@
     </row>
     <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1728</v>
+        <v>1736</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1024</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>14</v>
+        <v>1737</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1730</v>
+        <v>1024</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1731</v>
+        <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>1732</v>
+        <v>1739</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1733</v>
+        <v>1740</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1734</v>
+        <v>1741</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>1735</v>
+        <v>1742</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>985</v>
+        <v>1743</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1736</v>
+        <v>1744</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>1737</v>
+        <v>1745</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>985</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1738</v>
+        <v>1746</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>1739</v>
+        <v>1747</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>985</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>14</v>
+        <v>1748</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>1740</v>
+        <v>1749</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>1024</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>1741</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1742</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>1743</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>1744</v>
+        <v>1751</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1745</v>
+        <v>1752</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>14</v>
+        <v>1753</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -6535,66 +6576,66 @@
     </row>
     <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>1746</v>
+        <v>1754</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>961</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>1747</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>1748</v>
-      </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>995</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>1749</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>1751</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>1752</v>
+        <v>1759</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>1753</v>
+        <v>1760</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1754</v>
+        <v>1761</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>14</v>
+        <v>1762</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>1755</v>
+        <v>1763</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1754</v>
+        <v>1764</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>14</v>
@@ -6603,40 +6644,40 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1757</v>
+        <v>1764</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1758</v>
+        <v>14</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>14</v>
+        <v>1766</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>14</v>
+        <v>1767</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>14</v>
+        <v>1768</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>1759</v>
+        <v>14</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1760</v>
+        <v>14</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>14</v>
@@ -6645,12 +6686,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1761</v>
+        <v>1770</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>14</v>
@@ -6659,42 +6700,70 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1762</v>
+        <v>1771</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>14</v>
+        <v>1772</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>14</v>
+        <v>1774</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="41" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{E70BD82A-53AC-4758-97EB-B4C6645F72A7}"/>
+  <autoFilter ref="A1:D1" xr:uid="{C219768B-C22C-4C70-91C6-145F16566594}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E643B8-8F4F-4D75-BE9D-A92ACEEB2054}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5C1EF9-D8EB-4DCB-96C4-0A87CA67EC55}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6707,7 +6776,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1764</v>
+        <v>1777</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>75</v>
@@ -6716,16 +6785,16 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1765</v>
+        <v>1778</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1766</v>
+        <v>1779</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>89</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1767</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -6739,26 +6808,26 @@
         <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1768</v>
+        <v>1781</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1769</v>
+        <v>1782</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1770</v>
+        <v>1783</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{92E643B8-8F4F-4D75-BE9D-A92ACEEB2054}"/>
+  <autoFilter ref="A1:G1" xr:uid="{CF5C1EF9-D8EB-4DCB-96C4-0A87CA67EC55}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5EDCE7A-BE15-4EE7-9801-A3BABE344AEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FCB6F6-2699-4ACE-BB92-B6CBF9A6DC3E}">
   <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12290,13 +12359,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{A5EDCE7A-BE15-4EE7-9801-A3BABE344AEC}"/>
+  <autoFilter ref="A1:Q1" xr:uid="{09FCB6F6-2699-4ACE-BB92-B6CBF9A6DC3E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBC7781C-2E55-4564-810C-63806ADEEC37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D291DAA-BC83-42F0-821F-075A0C5100FE}">
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12987,13 +13056,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{CBC7781C-2E55-4564-810C-63806ADEEC37}"/>
+  <autoFilter ref="A1:H1" xr:uid="{1D291DAA-BC83-42F0-821F-075A0C5100FE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DC84AF4-E431-475D-B2D5-65F0F81B1195}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37EBF336-E5E5-4477-8065-E05C2239B3A9}">
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14201,13 +14270,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{7DC84AF4-E431-475D-B2D5-65F0F81B1195}"/>
+  <autoFilter ref="A1:H1" xr:uid="{37EBF336-E5E5-4477-8065-E05C2239B3A9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFA2E78-EAE7-4AB0-85F0-0B957AAF696D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFA61C4-3ED4-4740-AC4B-61B90C6CD6F5}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14687,13 +14756,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{6AFA2E78-EAE7-4AB0-85F0-0B957AAF696D}"/>
+  <autoFilter ref="A1:H1" xr:uid="{BEFA61C4-3ED4-4740-AC4B-61B90C6CD6F5}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2D31D2-8DFA-49C7-B653-63226AA85D40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C15D5A2-FABF-496C-9F2E-DD33DDE6A172}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15078,14 +15147,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{4C2D31D2-8DFA-49C7-B653-63226AA85D40}"/>
+  <autoFilter ref="A1:E1" xr:uid="{5C15D5A2-FABF-496C-9F2E-DD33DDE6A172}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7DA6D96-EBF0-47B5-9269-93067FFF07BF}">
-  <dimension ref="A1:G30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DD6E04-AD7B-4E39-A070-D795428BB3FC}">
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
@@ -15211,7 +15280,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="216" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1274</v>
       </c>
@@ -15786,14 +15855,37 @@
         <v>1436</v>
       </c>
     </row>
+    <row r="31" spans="1:7" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>1443</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{B7DA6D96-EBF0-47B5-9269-93067FFF07BF}"/>
+  <autoFilter ref="A1:G1" xr:uid="{54DD6E04-AD7B-4E39-A070-D795428BB3FC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4297D44A-1D2C-48D8-B47E-701F8AB50B4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15E0C12-9FB1-4353-AAA2-58C24AEBCF36}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15804,22 +15896,22 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1437</v>
+        <v>1444</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1438</v>
+        <v>1445</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1439</v>
+        <v>1446</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1440</v>
+        <v>1447</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1441</v>
+        <v>1448</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1442</v>
+        <v>1449</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1175</v>
@@ -15830,1260 +15922,1260 @@
     </row>
     <row r="2" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1445</v>
+        <v>1452</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1446</v>
+        <v>1453</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1447</v>
+        <v>1454</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1449</v>
+        <v>1456</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1450</v>
+        <v>1457</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1451</v>
+        <v>1458</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1453</v>
+        <v>1460</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1454</v>
+        <v>1461</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1455</v>
+        <v>1462</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1456</v>
+        <v>1463</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1457</v>
+        <v>1464</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1458</v>
+        <v>1465</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1461</v>
+        <v>1468</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1462</v>
+        <v>1469</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1463</v>
+        <v>1470</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1464</v>
+        <v>1471</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1466</v>
+        <v>1473</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1467</v>
+        <v>1474</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1468</v>
+        <v>1475</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1464</v>
+        <v>1471</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1470</v>
+        <v>1477</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1471</v>
+        <v>1478</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1466</v>
+        <v>1473</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1474</v>
+        <v>1481</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1475</v>
+        <v>1482</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1461</v>
+        <v>1468</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1477</v>
+        <v>1484</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1478</v>
+        <v>1485</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1480</v>
+        <v>1487</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1481</v>
+        <v>1488</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1482</v>
+        <v>1489</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1484</v>
+        <v>1491</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1485</v>
+        <v>1492</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1486</v>
+        <v>1493</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1466</v>
+        <v>1473</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1488</v>
+        <v>1495</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1489</v>
+        <v>1496</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1490</v>
+        <v>1497</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>1141</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1491</v>
+        <v>1498</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1492</v>
+        <v>1499</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1487</v>
+        <v>1494</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1483</v>
+        <v>1490</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1493</v>
+        <v>1500</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>1494</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>1495</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>1487</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1497</v>
+        <v>1504</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1498</v>
+        <v>1505</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1499</v>
+        <v>1506</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1473</v>
+        <v>1480</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1500</v>
+        <v>1507</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1501</v>
+        <v>1508</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1502</v>
+        <v>1509</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1460</v>
+        <v>1467</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>1274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1503</v>
+        <v>1510</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1504</v>
+        <v>1511</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1500</v>
+        <v>1507</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1507</v>
+        <v>1514</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1497</v>
+        <v>1504</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>1195</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1509</v>
+        <v>1516</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1510</v>
+        <v>1517</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1511</v>
+        <v>1518</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1512</v>
+        <v>1519</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1513</v>
+        <v>1520</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>1496</v>
+        <v>1503</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1514</v>
+        <v>1521</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1516</v>
+        <v>1523</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1520</v>
+        <v>1527</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1522</v>
+        <v>1529</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>1525</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>1526</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>1518</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>1517</v>
+        <v>1524</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1527</v>
+        <v>1534</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1528</v>
+        <v>1535</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1529</v>
+        <v>1536</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1532</v>
+        <v>1539</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1533</v>
+        <v>1540</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>1476</v>
+        <v>1483</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>1538</v>
+        <v>1545</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1539</v>
+        <v>1546</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1540</v>
+        <v>1547</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1541</v>
+        <v>1548</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1542</v>
+        <v>1549</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1543</v>
+        <v>1550</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>1531</v>
+        <v>1538</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1544</v>
+        <v>1551</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1545</v>
+        <v>1552</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>1546</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>1539</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1548</v>
+        <v>1555</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1549</v>
+        <v>1556</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1550</v>
+        <v>1557</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1469</v>
+        <v>1476</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1551</v>
+        <v>1558</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1552</v>
+        <v>1559</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1555</v>
+        <v>1562</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1556</v>
+        <v>1563</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1557</v>
+        <v>1564</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>1559</v>
+        <v>1566</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>1465</v>
+        <v>1472</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>1547</v>
+        <v>1554</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1560</v>
+        <v>1567</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1562</v>
+        <v>1569</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>1563</v>
+        <v>1570</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1565</v>
+        <v>1572</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1566</v>
+        <v>1573</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>1447</v>
+        <v>1454</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1569</v>
+        <v>1576</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1570</v>
+        <v>1577</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1571</v>
+        <v>1578</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>1179</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1572</v>
+        <v>1579</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1573</v>
+        <v>1580</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>1574</v>
+        <v>1581</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>1575</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>1576</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>1577</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>1568</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1578</v>
+        <v>1585</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1579</v>
+        <v>1586</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1580</v>
+        <v>1587</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>1581</v>
+        <v>1588</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>1204</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1583</v>
+        <v>1590</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>1584</v>
+        <v>1591</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>1585</v>
+        <v>1592</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1587</v>
+        <v>1594</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>1588</v>
+        <v>1595</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>1589</v>
+        <v>1596</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>1583</v>
+        <v>1590</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>1459</v>
+        <v>1466</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>1590</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>1591</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>1592</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>1583</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>1452</v>
+        <v>1459</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>1593</v>
+        <v>1600</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>1594</v>
+        <v>1601</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1595</v>
+        <v>1602</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>1590</v>
+        <v>1597</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>1597</v>
+        <v>1604</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1598</v>
+        <v>1605</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>1593</v>
+        <v>1600</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>1600</v>
+        <v>1607</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1601</v>
+        <v>1608</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="216" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>1602</v>
+        <v>1609</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>1603</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>1604</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>1596</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1605</v>
+        <v>1612</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>1606</v>
+        <v>1613</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1607</v>
+        <v>1614</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>1582</v>
+        <v>1589</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1608</v>
+        <v>1615</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>1609</v>
+        <v>1616</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1610</v>
+        <v>1617</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1611</v>
+        <v>1618</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>1216</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{4297D44A-1D2C-48D8-B47E-701F8AB50B4D}"/>
+  <autoFilter ref="A1:H1" xr:uid="{F15E0C12-9FB1-4353-AAA2-58C24AEBCF36}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD06967C-01FE-40CB-B6FA-EB46C4ACD459}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720786B-18C8-4D8D-A217-DDC3C3C168DF}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17095,19 +17187,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1612</v>
+        <v>1619</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1613</v>
+        <v>1620</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1614</v>
+        <v>1621</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1615</v>
+        <v>1622</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1616</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="144" x14ac:dyDescent="0.3">
@@ -17115,16 +17207,16 @@
         <v>420</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1617</v>
+        <v>1624</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1618</v>
+        <v>1625</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1619</v>
+        <v>1626</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1620</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
@@ -17132,16 +17224,16 @@
         <v>103</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1621</v>
+        <v>1628</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1622</v>
+        <v>1629</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1623</v>
+        <v>1630</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1624</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -17149,16 +17241,16 @@
         <v>389</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1625</v>
+        <v>1632</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1626</v>
+        <v>1633</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1627</v>
+        <v>1634</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1628</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -17166,13 +17258,13 @@
         <v>140</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1629</v>
+        <v>1636</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1630</v>
+        <v>1637</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
@@ -17183,13 +17275,13 @@
         <v>227</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1632</v>
+        <v>1639</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1633</v>
+        <v>1640</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1634</v>
+        <v>1641</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
@@ -17200,13 +17292,13 @@
         <v>176</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1635</v>
+        <v>1642</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1636</v>
+        <v>1643</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1637</v>
+        <v>1644</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
@@ -17217,13 +17309,13 @@
         <v>159</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1638</v>
+        <v>1645</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1639</v>
+        <v>1646</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1640</v>
+        <v>1647</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
@@ -17234,13 +17326,13 @@
         <v>553</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1641</v>
+        <v>1648</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1642</v>
+        <v>1649</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1643</v>
+        <v>1650</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
@@ -17251,13 +17343,13 @@
         <v>444</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1644</v>
+        <v>1651</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1645</v>
+        <v>1652</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1646</v>
+        <v>1653</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
@@ -17268,13 +17360,13 @@
         <v>430</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1647</v>
+        <v>1654</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1648</v>
+        <v>1655</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1649</v>
+        <v>1656</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
@@ -17282,13 +17374,13 @@
     </row>
     <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1651</v>
+        <v>1658</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1652</v>
+        <v>1659</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>96</v>
@@ -17299,16 +17391,16 @@
     </row>
     <row r="13" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1653</v>
+        <v>1660</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1654</v>
+        <v>1661</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1655</v>
+        <v>1662</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1656</v>
+        <v>1663</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
@@ -17316,16 +17408,16 @@
     </row>
     <row r="14" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1657</v>
+        <v>1664</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1658</v>
+        <v>1665</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1659</v>
+        <v>1666</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1660</v>
+        <v>1667</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
@@ -17333,16 +17425,16 @@
     </row>
     <row r="15" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1661</v>
+        <v>1668</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1662</v>
+        <v>1669</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1663</v>
+        <v>1670</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1664</v>
+        <v>1671</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
@@ -17353,16 +17445,16 @@
         <v>893</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1665</v>
+        <v>1672</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1666</v>
+        <v>1673</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1667</v>
+        <v>1674</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1668</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -17370,13 +17462,13 @@
         <v>890</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1670</v>
+        <v>1677</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1671</v>
+        <v>1678</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>14</v>
@@ -17384,16 +17476,16 @@
     </row>
     <row r="18" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1672</v>
+        <v>1679</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1673</v>
+        <v>1680</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1674</v>
+        <v>1681</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1675</v>
+        <v>1682</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>14</v>
@@ -17401,23 +17493,23 @@
     </row>
     <row r="19" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1676</v>
+        <v>1683</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1677</v>
+        <v>1684</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1678</v>
+        <v>1685</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1679</v>
+        <v>1686</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{DD06967C-01FE-40CB-B6FA-EB46C4ACD459}"/>
+  <autoFilter ref="A1:E1" xr:uid="{F720786B-18C8-4D8D-A217-DDC3C3C168DF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/design/TitlesMod-Design.xlsx
+++ b/design/TitlesMod-Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\IdeaProjects\TitlesMod\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{263BBEF4-E48C-4268-AC7C-1B61D6FC95D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BA2105B-EB3E-49C3-B00E-431FBF682AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5112" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{5BD3E99C-9A34-4EAF-96BE-896F56304FA0}"/>
+    <workbookView xWindow="5112" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{CA22B986-27D2-4854-9A3A-FA10050CCE84}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -24,11 +24,13 @@
     <sheet name="Open Questions" sheetId="9" r:id="rId9"/>
     <sheet name="Balance Model" sheetId="10" r:id="rId10"/>
     <sheet name="Tweak Queue" sheetId="11" r:id="rId11"/>
+    <sheet name="Integration Targets" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Balance Model'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Design Decisions'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Effect Catalog'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Integration Targets'!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Open Questions'!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Overview!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Progress Triggers'!$A$1:$H$1</definedName>
@@ -62,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3559" uniqueCount="1784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3760" uniqueCount="1923">
   <si>
     <t>Field</t>
   </si>
@@ -4204,7 +4206,7 @@
     <t>DECIDED - 1.20.1 on Forge 47.x</t>
   </si>
   <si>
-    <t>Every mod we want to integrate with ships Forge 1.20.1 only. Integration is the single requirement that cannot be solved in code - everything else can. 1.20.1 also still has one of the two largest modded player bases so this is not an exile to a dead version.</t>
+    <t>Every pack we want to slot into is 1.20.1 and three of the four are Forge - confirmed against Cisco's Dragonfyre manifest at forge-47.4.13. Prominence II is Fabric and is cut. Integration is the single requirement that cannot be solved in code - everything else can. 1.20.1 also still has one of the two largest modded player bases so this is not an exile to a dead version.</t>
   </si>
   <si>
     <t>Overrides the earlier NeoForge-only decision. Costs us Java 17 - obfuscated mappings - Capabilities instead of Attachments - and ForgeGradle. The eventual port crosses a loader change and five years of API churn at once.</t>
@@ -5101,6 +5103,9 @@
     <t>List each mod with its 1.20.1 Forge version and whether it exposes a real API or needs reflection</t>
   </si>
   <si>
+    <t>MOSTLY ANSWERED - see the Integration Targets sheet. Cisco's Dragonfyre read in full from its manifest - Soulrend and Beyond Depth partially. Answer - exactly TWO things need code - attributeslib as a compat class and a clean /titles grant command. Everything else is datapack JSON. Prominence II is CUT - it is a Fabric pack and Sinytra Connector cannot run a Forge mod on Fabric. Still open - read the Soulrend and Beyond Depth manifests to confirm</t>
+  </si>
+  <si>
     <t>17</t>
   </si>
   <si>
@@ -5113,6 +5118,9 @@
     <t>Check each one on Modrinth and CurseForge before committing to the port</t>
   </si>
   <si>
+    <t>MUCH SMALLER NOW - only attributeslib actually matters since it is our one compat class. Everything else is datapack JSON that survives the port untouched regardless of what those mods do</t>
+  </si>
+  <si>
     <t>18</t>
   </si>
   <si>
@@ -5125,6 +5133,24 @@
     <t>All soft / one is effectively required</t>
   </si>
   <si>
+    <t>ANSWERED - all soft. Nothing is required. The two things that need code both degrade cleanly - the attributeslib effects skip silently when it is absent and the command works standalone</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Does Epic Fight bypass vanilla attack attributes?</t>
+  </si>
+  <si>
+    <t>Soulrend is built on Epic Fight. If it handles damage without consulting attack_damage then every damage title is silently inert in that pack and no amount of balancing fixes it</t>
+  </si>
+  <si>
+    <t>Test in-game once we have a working build / find another lever for that pack / accept damage titles do nothing there</t>
+  </si>
+  <si>
+    <t>The single highest-risk unknown on the Integration Targets sheet. Cannot be resolved on paper</t>
+  </si>
+  <si>
     <t>Rule</t>
   </si>
   <si>
@@ -5414,6 +5440,399 @@
   </si>
   <si>
     <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>Mod or Group</t>
+  </si>
+  <si>
+    <t>Registry Namespace</t>
+  </si>
+  <si>
+    <t>Seen In</t>
+  </si>
+  <si>
+    <t>Why It Matters To Us</t>
+  </si>
+  <si>
+    <t>Integration Type</t>
+  </si>
+  <si>
+    <t>What We Actually Do</t>
+  </si>
+  <si>
+    <t>PROVENANCE</t>
+  </si>
+  <si>
+    <t>Cisco's Dragonfyre was read from its CurseForge instance manifest on 2026-08-25 - MC 1.20.1 - forge-47.4.13 - 375 mods. The full list is in design/reference/cisco-dragonfyre-modlist.txt. Soulrend and Beyond Depth come from their CurseForge store pages plus one page of Soulrend's 468-entry relations list - NOT full manifests.</t>
+  </si>
+  <si>
+    <t>Treat every Soulrend and Beyond Depth row as provisional until we read their manifests</t>
+  </si>
+  <si>
+    <t>To capture a pack cheaply download the modpack zip from its Files tab instead of installing it - a few hundred KB containing manifest.json and modlist.html</t>
+  </si>
+  <si>
+    <t>LEGEND - FREE</t>
+  </si>
+  <si>
+    <t>A generic datapack condition keyed on a registry id or tag reaches this mod's content with no dependency and no code. The condition is simply never satisfied when the mod is absent.</t>
+  </si>
+  <si>
+    <t>Nothing. Write the title JSON.</t>
+  </si>
+  <si>
+    <t>This is the overwhelming majority of integration and it is why the datapack vocabulary matters more than any Java compat class</t>
+  </si>
+  <si>
+    <t>LEGEND - COMMAND</t>
+  </si>
+  <si>
+    <t>The pack author drives us. Their quest or script calls our command as a reward.</t>
+  </si>
+  <si>
+    <t>Keep the command surface clean and scriptable</t>
+  </si>
+  <si>
+    <t>Zero code on either side. Probably our single highest-value integration path</t>
+  </si>
+  <si>
+    <t>LEGEND - COMPAT CLASS</t>
+  </si>
+  <si>
+    <t>We want to read or write something only this mod defines.</t>
+  </si>
+  <si>
+    <t>One isolated class behind a ModList.get().isLoaded() guard - never referenced from a field type in a loaded class</t>
+  </si>
+  <si>
+    <t>Per the Integration dependencies decision. Core must load and play correctly with it absent</t>
+  </si>
+  <si>
+    <t>LEGEND - WATCH</t>
+  </si>
+  <si>
+    <t>Grants attributes of its own. Does not need code from us - it needs our additive-only rule to be correct.</t>
+  </si>
+  <si>
+    <t>Nothing. Listed so we remember why the Stacking with other mods rule exists</t>
+  </si>
+  <si>
+    <t>See the Balance Model sheet</t>
+  </si>
+  <si>
+    <t>LEGEND - VERIFY</t>
+  </si>
+  <si>
+    <t>Alters the damage or attribute pipeline in a way that could make our numbers behave differently than we expect.</t>
+  </si>
+  <si>
+    <t>Test in-game before trusting any balance number</t>
+  </si>
+  <si>
+    <t>Cannot be resolved on paper</t>
+  </si>
+  <si>
+    <t>Apotheosis and Apothic Attributes</t>
+  </si>
+  <si>
+    <t>attributeslib</t>
+  </si>
+  <si>
+    <t>Cisco's and Soulrend</t>
+  </si>
+  <si>
+    <t>Registers 21 real attributes on 1.20.1 - crit_chance - crit_damage - life_steal - overheal - ghost_health - armor_pierce - armor_shred - prot_pierce - prot_shred - dodge_chance - draw_speed - arrow_damage - arrow_velocity - current_hp_damage - fire_damage - cold_damage - healing_received - mining_speed - experience_gained - elytra_flight - creative_flight</t>
+  </si>
+  <si>
+    <t>COMPAT CLASS</t>
+  </si>
+  <si>
+    <t>One compat class letting title effects target attributeslib attributes when it is loaded. Skip the effect silently when it is not.</t>
+  </si>
+  <si>
+    <t>THE most valuable single integration - present in both packs we have data for. mining_speed and experience_gained also map onto effects the Effect Catalog currently has to implement with event hooks. Namespace is attributeslib NOT apothic_attributes - verified against ALObjects.java on the 1.20 branch</t>
+  </si>
+  <si>
+    <t>AttributeFix</t>
+  </si>
+  <si>
+    <t>attributefix</t>
+  </si>
+  <si>
+    <t>Cisco's</t>
+  </si>
+  <si>
+    <t>Raises or removes the hard-coded min and max bounds vanilla puts on attributes. Its presence is direct evidence that this pack expects inflated attribute totals.</t>
+  </si>
+  <si>
+    <t>WATCH</t>
+  </si>
+  <si>
+    <t>Nothing - but config validation must not accept a cap value that vanilla would silently clamp when AttributeFix is absent</t>
+  </si>
+  <si>
+    <t>The clearest single proof that clamping the player's final attribute value would have been the wrong design</t>
+  </si>
+  <si>
+    <t>Passive Skill Trees</t>
+  </si>
+  <si>
+    <t>skilltree</t>
+  </si>
+  <si>
+    <t>Grants attributes directly through a skill tree. Stacks with everything else.</t>
+  </si>
+  <si>
+    <t>Nothing</t>
+  </si>
+  <si>
+    <t>One of four separate attribute sources in Cisco's alone</t>
+  </si>
+  <si>
+    <t>Just Leveling</t>
+  </si>
+  <si>
+    <t>Soulrend</t>
+  </si>
+  <si>
+    <t>Levelling system granting attribute points as the player levels</t>
+  </si>
+  <si>
+    <t>A level-50 Soulrend player may sit far above vanilla baselines before our mod does anything</t>
+  </si>
+  <si>
+    <t>Origins family</t>
+  </si>
+  <si>
+    <t>origins</t>
+  </si>
+  <si>
+    <t>Origins (Forge) plus Origins Classes plus Medieval Origins Revival plus Strictly Origins. Grants powers - some attribute-backed.</t>
+  </si>
+  <si>
+    <t>Nothing for v1</t>
+  </si>
+  <si>
+    <t>An origin-gated title condition is possible later but is not worth a compat class yet</t>
+  </si>
+  <si>
+    <t>Better Combat</t>
+  </si>
+  <si>
+    <t>bettercombat</t>
+  </si>
+  <si>
+    <t>Combat overhaul changing attack handling and reach</t>
+  </si>
+  <si>
+    <t>VERIFY</t>
+  </si>
+  <si>
+    <t>Confirm attack_damage and attack_speed modifiers flow through as expected</t>
+  </si>
+  <si>
+    <t>The pack also ships a Better Combat x Apotheosis Compat mod - the author has already had to reconcile two attribute systems by hand. Staying additive-only keeps us off that list</t>
+  </si>
+  <si>
+    <t>Epic Fight</t>
+  </si>
+  <si>
+    <t>epicfight</t>
+  </si>
+  <si>
+    <t>Full combat overhaul with its own movesets and damage handling</t>
+  </si>
+  <si>
+    <t>Confirm our attribute modifiers are respected at all</t>
+  </si>
+  <si>
+    <t>The highest-risk unknown on this sheet. If Epic Fight bypasses vanilla attack attributes then damage titles are inert in Soulrend and that pack needs a different lever</t>
+  </si>
+  <si>
+    <t>FTB Quests and FTB Library</t>
+  </si>
+  <si>
+    <t>ftbquests</t>
+  </si>
+  <si>
+    <t>Cisco's - Soulrend - Beyond Depth</t>
+  </si>
+  <si>
+    <t>Quest system with command rewards. Every pack we target runs a quest system.</t>
+  </si>
+  <si>
+    <t>COMMAND</t>
+  </si>
+  <si>
+    <t>Keep /titles grant clean - scriptable - and safe to call from a quest reward</t>
+  </si>
+  <si>
+    <t>Lets a pack author award our titles as quest rewards with no code from either side. Cheapest and most likely-used path we have</t>
+  </si>
+  <si>
+    <t>L_Ender's Cataclysm</t>
+  </si>
+  <si>
+    <t>cataclysm</t>
+  </si>
+  <si>
+    <t>Boss and mob content in all three target packs</t>
+  </si>
+  <si>
+    <t>FREE</t>
+  </si>
+  <si>
+    <t>Title JSON keyed on entity ids</t>
+  </si>
+  <si>
+    <t>Appears in every pack we have looked at - strongest candidate for shipping example title JSON</t>
+  </si>
+  <si>
+    <t>Mowzie's Mobs</t>
+  </si>
+  <si>
+    <t>mowziesmobs</t>
+  </si>
+  <si>
+    <t>Boss content in all three target packs</t>
+  </si>
+  <si>
+    <t>Same as Cataclysm</t>
+  </si>
+  <si>
+    <t>Alex's Mobs and Alex's Caves</t>
+  </si>
+  <si>
+    <t>alexsmobs and alexscaves</t>
+  </si>
+  <si>
+    <t>Large mob and biome content</t>
+  </si>
+  <si>
+    <t>Title JSON keyed on entity - biome and item ids</t>
+  </si>
+  <si>
+    <t>Bosses of Mass Destruction and Bosses Rise</t>
+  </si>
+  <si>
+    <t>bosses_of_mass_destruction</t>
+  </si>
+  <si>
+    <t>Additional named boss fights</t>
+  </si>
+  <si>
+    <t>Mutant Monsters</t>
+  </si>
+  <si>
+    <t>mutantmonsters</t>
+  </si>
+  <si>
+    <t>Upgraded vanilla mob variants</t>
+  </si>
+  <si>
+    <t>Marium's Soulslike Weaponry</t>
+  </si>
+  <si>
+    <t>soulslikeweaponry</t>
+  </si>
+  <si>
+    <t>Weapon content with unique mechanics</t>
+  </si>
+  <si>
+    <t>Title JSON keyed on item ids and kill-with-item conditions</t>
+  </si>
+  <si>
+    <t>Irons Spells n Spellbooks and Ars Elemental</t>
+  </si>
+  <si>
+    <t>irons_spellbooks and ars_elemental</t>
+  </si>
+  <si>
+    <t>Magic systems with their own progression</t>
+  </si>
+  <si>
+    <t>FREE for v1</t>
+  </si>
+  <si>
+    <t>Title JSON keyed on item and entity ids</t>
+  </si>
+  <si>
+    <t>A spell-cast-count condition would need a compat class. Not worth it until someone asks for it</t>
+  </si>
+  <si>
+    <t>The Twilight Forest and The Aether</t>
+  </si>
+  <si>
+    <t>twilightforest and aether</t>
+  </si>
+  <si>
+    <t>Full extra dimensions</t>
+  </si>
+  <si>
+    <t>Title JSON keyed on dimension ids</t>
+  </si>
+  <si>
+    <t>The Undergarden - Deeper and Darker - Voidscape</t>
+  </si>
+  <si>
+    <t>Beyond Depth</t>
+  </si>
+  <si>
+    <t>Three extra dimensions</t>
+  </si>
+  <si>
+    <t>From the Beyond Depth store page - provisional until we read its manifest</t>
+  </si>
+  <si>
+    <t>Structure mod family</t>
+  </si>
+  <si>
+    <t>Cisco's and Beyond Depth</t>
+  </si>
+  <si>
+    <t>When Dungeons Arise - Dungeons Plus - Dungeon Crawl - Dungeons Enhanced - Stalwart Dungeons - YUNGs Better Dungeons - Explorify</t>
+  </si>
+  <si>
+    <t>Title JSON keyed on structure ids or tags</t>
+  </si>
+  <si>
+    <t>A reach-a-structure condition covers all of these at once if we key on tags wherever possible</t>
+  </si>
+  <si>
+    <t>Sinytra Connector and Forgified Fabric API and Architectury</t>
+  </si>
+  <si>
+    <t>Lets the pack run Fabric mods on Forge</t>
+  </si>
+  <si>
+    <t>NO ACTION</t>
+  </si>
+  <si>
+    <t>Connector goes Fabric to Forge only - never the reverse. This is why a Forge mod is the correct shape for Cisco's - and why Prominence II being a Fabric pack cannot be solved this way</t>
+  </si>
+  <si>
+    <t>CONCLUSION - what actually needs code</t>
+  </si>
+  <si>
+    <t>Exactly two things - attributeslib as a compat class and a clean /titles grant command. Everything else on this sheet is datapack JSON or nothing at all.</t>
+  </si>
+  <si>
+    <t>Prioritise the condition and effect vocabulary over any per-mod Java</t>
+  </si>
+  <si>
+    <t>The mods worth a compat class are the ones appearing in EVERY target pack. There are two of them. Resist adding more</t>
+  </si>
+  <si>
+    <t>CONCLUSION - what to build for pack authors</t>
+  </si>
+  <si>
+    <t>Ship example title JSON for Cataclysm and Mowzies since they appear in all three packs - and document the condition vocabulary properly</t>
+  </si>
+  <si>
+    <t>A pack author who can write their own titles is worth more than any compat class we write for them</t>
+  </si>
+  <si>
+    <t>Also port-proof - JSON survives the jump to 26.x untouched while every Java compat class is a liability</t>
   </si>
 </sst>
 </file>
@@ -5870,7 +6289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{768CCA91-BABD-464E-8EB5-4030549F8955}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36E9414-1507-41FE-B199-442930F37D0F}">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6153,13 +6572,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{768CCA91-BABD-464E-8EB5-4030549F8955}"/>
+  <autoFilter ref="A1:C1" xr:uid="{A36E9414-1507-41FE-B199-442930F37D0F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C219768B-C22C-4C70-91C6-145F16566594}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258A1ABF-5747-4C43-B595-EDB8A92217E7}">
   <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6170,13 +6589,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1687</v>
+        <v>1695</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1688</v>
+        <v>1696</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>14</v>
@@ -6190,7 +6609,7 @@
         <v>430</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1689</v>
+        <v>1697</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>14</v>
@@ -6198,13 +6617,13 @@
     </row>
     <row r="3" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1691</v>
+        <v>1699</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1692</v>
+        <v>1700</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -6212,13 +6631,13 @@
     </row>
     <row r="4" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1693</v>
+        <v>1701</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1694</v>
+        <v>1702</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1695</v>
+        <v>1703</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>14</v>
@@ -6229,10 +6648,10 @@
         <v>1267</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1696</v>
+        <v>1704</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1697</v>
+        <v>1705</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>14</v>
@@ -6240,13 +6659,13 @@
     </row>
     <row r="6" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1698</v>
+        <v>1706</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1699</v>
+        <v>1707</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1700</v>
+        <v>1708</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>14</v>
@@ -6254,13 +6673,13 @@
     </row>
     <row r="7" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1701</v>
+        <v>1709</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1702</v>
+        <v>1710</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1703</v>
+        <v>1711</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -6268,13 +6687,13 @@
     </row>
     <row r="8" spans="1:4" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1704</v>
+        <v>1712</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1705</v>
+        <v>1713</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1706</v>
+        <v>1714</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -6282,13 +6701,13 @@
     </row>
     <row r="9" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1707</v>
+        <v>1715</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1708</v>
+        <v>1716</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1709</v>
+        <v>1717</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -6296,13 +6715,13 @@
     </row>
     <row r="10" spans="1:4" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1710</v>
+        <v>1718</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1711</v>
+        <v>1719</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1712</v>
+        <v>1720</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -6324,13 +6743,13 @@
     </row>
     <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1713</v>
+        <v>1721</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1715</v>
+        <v>1723</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -6338,13 +6757,13 @@
     </row>
     <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1716</v>
+        <v>1724</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1717</v>
+        <v>1725</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1718</v>
+        <v>1726</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -6352,13 +6771,13 @@
     </row>
     <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1719</v>
+        <v>1727</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1720</v>
+        <v>1728</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1721</v>
+        <v>1729</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -6366,13 +6785,13 @@
     </row>
     <row r="15" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1722</v>
+        <v>1730</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1723</v>
+        <v>1731</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1724</v>
+        <v>1732</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>14</v>
@@ -6380,13 +6799,13 @@
     </row>
     <row r="16" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1725</v>
+        <v>1733</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1726</v>
+        <v>1734</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1727</v>
+        <v>1735</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>14</v>
@@ -6394,13 +6813,13 @@
     </row>
     <row r="17" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1728</v>
+        <v>1736</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1729</v>
+        <v>1737</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1730</v>
+        <v>1738</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>14</v>
@@ -6422,10 +6841,10 @@
     </row>
     <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1731</v>
+        <v>1739</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1732</v>
+        <v>1740</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>939</v>
@@ -6436,13 +6855,13 @@
     </row>
     <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>1733</v>
+        <v>1741</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1734</v>
+        <v>1742</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1735</v>
+        <v>1743</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>14</v>
@@ -6450,13 +6869,13 @@
     </row>
     <row r="21" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1736</v>
+        <v>1744</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>1024</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1737</v>
+        <v>1745</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>14</v>
@@ -6464,7 +6883,7 @@
     </row>
     <row r="22" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>1738</v>
+        <v>1746</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>1024</v>
@@ -6478,13 +6897,13 @@
     </row>
     <row r="23" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>1739</v>
+        <v>1747</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1740</v>
+        <v>1748</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1741</v>
+        <v>1749</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>14</v>
@@ -6492,13 +6911,13 @@
     </row>
     <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>1742</v>
+        <v>1750</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1743</v>
+        <v>1751</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1744</v>
+        <v>1752</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>14</v>
@@ -6506,13 +6925,13 @@
     </row>
     <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>1745</v>
+        <v>1753</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>985</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1746</v>
+        <v>1754</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>14</v>
@@ -6520,13 +6939,13 @@
     </row>
     <row r="26" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>1747</v>
+        <v>1755</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>985</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1748</v>
+        <v>1756</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>14</v>
@@ -6534,7 +6953,7 @@
     </row>
     <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>1749</v>
+        <v>1757</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>985</v>
@@ -6548,7 +6967,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>1750</v>
+        <v>1758</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>1024</v>
@@ -6562,13 +6981,13 @@
     </row>
     <row r="29" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>1751</v>
+        <v>1759</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1752</v>
+        <v>1760</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1753</v>
+        <v>1761</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>14</v>
@@ -6576,10 +6995,10 @@
     </row>
     <row r="30" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>1754</v>
+        <v>1762</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1755</v>
+        <v>1763</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>14</v>
@@ -6590,13 +7009,13 @@
     </row>
     <row r="31" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1756</v>
+        <v>1764</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>961</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1757</v>
+        <v>1765</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>14</v>
@@ -6604,13 +7023,13 @@
     </row>
     <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>1758</v>
+        <v>1766</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>995</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>1759</v>
+        <v>1767</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>14</v>
@@ -6618,13 +7037,13 @@
     </row>
     <row r="33" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>1760</v>
+        <v>1768</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1761</v>
+        <v>1769</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>1762</v>
+        <v>1770</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>14</v>
@@ -6632,10 +7051,10 @@
     </row>
     <row r="34" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>1763</v>
+        <v>1771</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>14</v>
@@ -6646,10 +7065,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>1765</v>
+        <v>1773</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>14</v>
@@ -6660,13 +7079,13 @@
     </row>
     <row r="36" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>1766</v>
+        <v>1774</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>1767</v>
+        <v>1775</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1768</v>
+        <v>1776</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>14</v>
@@ -6688,10 +7107,10 @@
     </row>
     <row r="38" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1770</v>
+        <v>1778</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>14</v>
@@ -6702,13 +7121,13 @@
     </row>
     <row r="39" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>1771</v>
+        <v>1779</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>1772</v>
+        <v>1780</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>14</v>
@@ -6716,13 +7135,13 @@
     </row>
     <row r="40" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1773</v>
+        <v>1781</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1774</v>
+        <v>1782</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>14</v>
@@ -6730,10 +7149,10 @@
     </row>
     <row r="41" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>1775</v>
+        <v>1783</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>14</v>
@@ -6744,10 +7163,10 @@
     </row>
     <row r="42" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>1776</v>
+        <v>1784</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>14</v>
@@ -6757,13 +7176,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{C219768B-C22C-4C70-91C6-145F16566594}"/>
+  <autoFilter ref="A1:D1" xr:uid="{258A1ABF-5747-4C43-B595-EDB8A92217E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5C1EF9-D8EB-4DCB-96C4-0A87CA67EC55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D736BB-E499-4EDC-9E1F-CFE025B6BF31}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6776,7 +7195,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1777</v>
+        <v>1785</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>75</v>
@@ -6785,16 +7204,16 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1778</v>
+        <v>1786</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1779</v>
+        <v>1787</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>89</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1780</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="72" x14ac:dyDescent="0.3">
@@ -6808,26 +7227,690 @@
         <v>96</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1781</v>
+        <v>1789</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>96</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>1782</v>
+        <v>1790</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1783</v>
+        <v>1791</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{CF5C1EF9-D8EB-4DCB-96C4-0A87CA67EC55}"/>
+  <autoFilter ref="A1:G1" xr:uid="{E1D736BB-E499-4EDC-9E1F-CFE025B6BF31}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{481FF3C1-0E29-460C-A44C-F53E065B77E4}">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="216" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{481FF3C1-0E29-460C-A44C-F53E065B77E4}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09FCB6F6-2699-4ACE-BB92-B6CBF9A6DC3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48CCB69A-E489-4474-8A32-E59654D5B332}">
   <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12359,13 +13442,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{09FCB6F6-2699-4ACE-BB92-B6CBF9A6DC3E}"/>
+  <autoFilter ref="A1:Q1" xr:uid="{48CCB69A-E489-4474-8A32-E59654D5B332}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D291DAA-BC83-42F0-821F-075A0C5100FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE02F57-E7DC-416C-8FC9-E22D39861831}">
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13056,13 +14139,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{1D291DAA-BC83-42F0-821F-075A0C5100FE}"/>
+  <autoFilter ref="A1:H1" xr:uid="{AFE02F57-E7DC-416C-8FC9-E22D39861831}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37EBF336-E5E5-4477-8065-E05C2239B3A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E92F506-C0AD-4FDD-8814-AB63D37ED662}">
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14270,13 +15353,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{37EBF336-E5E5-4477-8065-E05C2239B3A9}"/>
+  <autoFilter ref="A1:H1" xr:uid="{0E92F506-C0AD-4FDD-8814-AB63D37ED662}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEFA61C4-3ED4-4740-AC4B-61B90C6CD6F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A44C572-131D-44C1-8CEA-FA86469E3B4E}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14756,13 +15839,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{BEFA61C4-3ED4-4740-AC4B-61B90C6CD6F5}"/>
+  <autoFilter ref="A1:H1" xr:uid="{2A44C572-131D-44C1-8CEA-FA86469E3B4E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C15D5A2-FABF-496C-9F2E-DD33DDE6A172}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8513E5B-B681-4E6A-8167-A344986C3D21}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15147,13 +16230,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{5C15D5A2-FABF-496C-9F2E-DD33DDE6A172}"/>
+  <autoFilter ref="A1:E1" xr:uid="{E8513E5B-B681-4E6A-8167-A344986C3D21}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DD6E04-AD7B-4E39-A070-D795428BB3FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184E8F60-124B-41FC-9457-DC42B2E004EB}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15161,7 +16244,7 @@
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.77734375" customWidth="1"/>
     <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15211,7 +16294,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1254</v>
       </c>
@@ -15257,7 +16340,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1267</v>
       </c>
@@ -15280,7 +16363,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1274</v>
       </c>
@@ -15303,7 +16386,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1280</v>
       </c>
@@ -15326,7 +16409,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1287</v>
       </c>
@@ -15349,7 +16432,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="360" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1294</v>
       </c>
@@ -15372,7 +16455,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1301</v>
       </c>
@@ -15395,7 +16478,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1307</v>
       </c>
@@ -15441,7 +16524,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>1321</v>
       </c>
@@ -15464,7 +16547,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1327</v>
       </c>
@@ -15487,7 +16570,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1334</v>
       </c>
@@ -15510,7 +16593,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="144" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1341</v>
       </c>
@@ -15533,7 +16616,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1348</v>
       </c>
@@ -15648,7 +16731,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>1375</v>
       </c>
@@ -15671,7 +16754,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>1382</v>
       </c>
@@ -15694,7 +16777,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="216" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>1389</v>
       </c>
@@ -15740,7 +16823,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>1403</v>
       </c>
@@ -15763,7 +16846,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>1410</v>
       </c>
@@ -15786,7 +16869,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>1417</v>
       </c>
@@ -15809,7 +16892,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="288" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>1423</v>
       </c>
@@ -15832,7 +16915,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>1430</v>
       </c>
@@ -15855,7 +16938,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="360" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1437</v>
       </c>
@@ -15879,13 +16962,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{54DD6E04-AD7B-4E39-A070-D795428BB3FC}"/>
+  <autoFilter ref="A1:G1" xr:uid="{184E8F60-124B-41FC-9457-DC42B2E004EB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F15E0C12-9FB1-4353-AAA2-58C24AEBCF36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE481AD0-D06D-45B6-942A-385A9594135C}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17169,20 +18252,20 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{F15E0C12-9FB1-4353-AAA2-58C24AEBCF36}"/>
+  <autoFilter ref="A1:H1" xr:uid="{CE481AD0-D06D-45B6-942A-385A9594135C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720786B-18C8-4D8D-A217-DDC3C3C168DF}">
-  <dimension ref="A1:E19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9B2B16-048D-4ED1-B895-B90C6006F60D}">
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="10.77734375" customWidth="1"/>
     <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -17202,7 +18285,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>420</v>
       </c>
@@ -17219,7 +18302,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>103</v>
       </c>
@@ -17236,7 +18319,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>389</v>
       </c>
@@ -17440,7 +18523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>893</v>
       </c>
@@ -17457,7 +18540,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>890</v>
       </c>
@@ -17471,45 +18554,62 @@
         <v>1678</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>14</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>14</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>14</v>
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="216" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1694</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{F720786B-18C8-4D8D-A217-DDC3C3C168DF}"/>
+  <autoFilter ref="A1:E1" xr:uid="{6F9B2B16-048D-4ED1-B895-B90C6006F60D}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/design/TitlesMod-Design.xlsx
+++ b/design/TitlesMod-Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\IdeaProjects\TitlesMod\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3BA2105B-EB3E-49C3-B00E-431FBF682AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{852F5E69-9E51-4409-B7A7-6753D8C09D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5112" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{CA22B986-27D2-4854-9A3A-FA10050CCE84}"/>
+    <workbookView xWindow="5112" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{2B6B08A0-D99A-4FBE-A4B8-D7F51C61483B}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -4644,7 +4644,7 @@
     <t>Server ledger</t>
   </si>
   <si>
-    <t>SavedData tracking Limited and Unique claims plus last-seen timestamps</t>
+    <t>Append-only SavedData tracking Limited - Founding - Unique and Contested claims. No last-seen timestamps - nothing is ever released so they are never read</t>
   </si>
   <si>
     <t>Ledger persists across restarts</t>
@@ -4659,13 +4659,13 @@
     <t>No double-grants under race</t>
   </si>
   <si>
-    <t>Release sweep</t>
-  </si>
-  <si>
-    <t>Daily sweep releasing titles from long-inactive holders</t>
-  </si>
-  <si>
-    <t>Latecomers can chase Limited titles</t>
+    <t>Contested transfer</t>
+  </si>
+  <si>
+    <t>Score-beats-holder takeover for Contested titles - the only revocable scarcity type. Never on death and never on inactivity</t>
+  </si>
+  <si>
+    <t>The Unrivaled changes hands only when someone beats the score</t>
   </si>
   <si>
     <t>Ledger UI</t>
@@ -6289,7 +6289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36E9414-1507-41FE-B199-442930F37D0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0695F88D-2251-4452-ADB7-A833A1F80A7F}">
   <dimension ref="A1:C25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6572,13 +6572,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C1" xr:uid="{A36E9414-1507-41FE-B199-442930F37D0F}"/>
+  <autoFilter ref="A1:C1" xr:uid="{0695F88D-2251-4452-ADB7-A833A1F80A7F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{258A1ABF-5747-4C43-B595-EDB8A92217E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56F1EEEC-C9A8-4474-98CA-AB18E193254C}">
   <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7176,13 +7176,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{258A1ABF-5747-4C43-B595-EDB8A92217E7}"/>
+  <autoFilter ref="A1:D1" xr:uid="{56F1EEEC-C9A8-4474-98CA-AB18E193254C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D736BB-E499-4EDC-9E1F-CFE025B6BF31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C992350-FB65-4B54-9DDD-87E7A3F8BB41}">
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7240,13 +7240,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{E1D736BB-E499-4EDC-9E1F-CFE025B6BF31}"/>
+  <autoFilter ref="A1:G1" xr:uid="{0C992350-FB65-4B54-9DDD-87E7A3F8BB41}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{481FF3C1-0E29-460C-A44C-F53E065B77E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A60416-8C94-4039-B79F-9FC745818C7C}">
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7904,13 +7904,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{481FF3C1-0E29-460C-A44C-F53E065B77E4}"/>
+  <autoFilter ref="A1:G1" xr:uid="{30A60416-8C94-4039-B79F-9FC745818C7C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48CCB69A-E489-4474-8A32-E59654D5B332}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FB977C9-040A-4C95-BE5D-44270507B9D8}">
   <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13442,13 +13442,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{48CCB69A-E489-4474-8A32-E59654D5B332}"/>
+  <autoFilter ref="A1:Q1" xr:uid="{8FB977C9-040A-4C95-BE5D-44270507B9D8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE02F57-E7DC-416C-8FC9-E22D39861831}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C5910A-D221-4564-B410-2A9DA9866023}">
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14139,13 +14139,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{AFE02F57-E7DC-416C-8FC9-E22D39861831}"/>
+  <autoFilter ref="A1:H1" xr:uid="{85C5910A-D221-4564-B410-2A9DA9866023}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E92F506-C0AD-4FDD-8814-AB63D37ED662}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357492CC-8CCD-4773-BB2A-C85A610D7D53}">
   <dimension ref="A1:H46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15353,13 +15353,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{0E92F506-C0AD-4FDD-8814-AB63D37ED662}"/>
+  <autoFilter ref="A1:H1" xr:uid="{357492CC-8CCD-4773-BB2A-C85A610D7D53}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A44C572-131D-44C1-8CEA-FA86469E3B4E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00877D96-D750-4FC6-B5F4-99811411F11A}">
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15839,13 +15839,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{2A44C572-131D-44C1-8CEA-FA86469E3B4E}"/>
+  <autoFilter ref="A1:H1" xr:uid="{00877D96-D750-4FC6-B5F4-99811411F11A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8513E5B-B681-4E6A-8167-A344986C3D21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD22849-313C-4951-A781-8DF4AE51A0C2}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16230,13 +16230,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{E8513E5B-B681-4E6A-8167-A344986C3D21}"/>
+  <autoFilter ref="A1:E1" xr:uid="{9FD22849-313C-4951-A781-8DF4AE51A0C2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184E8F60-124B-41FC-9457-DC42B2E004EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2069EE06-F3A2-4A71-9ADB-E58B981251AE}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16962,13 +16962,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{184E8F60-124B-41FC-9457-DC42B2E004EB}"/>
+  <autoFilter ref="A1:G1" xr:uid="{2069EE06-F3A2-4A71-9ADB-E58B981251AE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE481AD0-D06D-45B6-942A-385A9594135C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D719F90B-D691-4214-B12A-E5DD09CE79F0}">
   <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -17549,7 +17549,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>1524</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>1524</v>
       </c>
@@ -18252,13 +18252,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{CE481AD0-D06D-45B6-942A-385A9594135C}"/>
+  <autoFilter ref="A1:H1" xr:uid="{D719F90B-D691-4214-B12A-E5DD09CE79F0}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F9B2B16-048D-4ED1-B895-B90C6006F60D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCEA78DE-E434-4753-AF33-C69E10F5DC44}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -18609,7 +18609,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{6F9B2B16-048D-4ED1-B895-B90C6006F60D}"/>
+  <autoFilter ref="A1:E1" xr:uid="{BCEA78DE-E434-4753-AF33-C69E10F5DC44}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>